--- a/frontend/e2e/fixtures/ordenes-validas.xlsx
+++ b/frontend/e2e/fixtures/ordenes-validas.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>sku_interno</t>
+          <t>sku</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">

--- a/frontend/e2e/fixtures/ordenes-validas.xlsx
+++ b/frontend/e2e/fixtures/ordenes-validas.xlsx
@@ -466,11 +466,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>E2E-MASA</t>
+          <t>PT-020-DONA</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
@@ -498,11 +498,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>E2E-MASA</t>
+          <t>PT-020-DONA</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>E2E-MASA</t>
+          <t>PT-020-DONA</t>
         </is>
       </c>
       <c r="C4" t="n">

--- a/frontend/e2e/fixtures/ordenes-validas.xlsx
+++ b/frontend/e2e/fixtures/ordenes-validas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,25 +434,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>area</t>
+          <t>turno</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>turno</t>
+          <t>ubicacion</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>ubicacion</t>
+          <t>notas</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
-        <is>
-          <t>notas</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
         <is>
           <t>comentario</t>
         </is>
@@ -472,19 +467,18 @@
       <c r="C2" t="n">
         <v>12</v>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Día</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>E2E 8</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
-        <is>
-          <t>E2E 8</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
         <is>
           <t>se ignora</t>
         </is>
@@ -504,19 +498,18 @@
       <c r="C3" t="n">
         <v>8</v>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Día</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
         <is>
           <t>E2E 8</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -534,13 +527,12 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>E2E 8</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
